--- a/input/Domains/Common/StringTable.xlsx
+++ b/input/Domains/Common/StringTable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Game/strings/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Common/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE444B2-462E-6A40-BAA5-3A78437AEA2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702233DE-44E9-B34C-B4BD-9F0B88918A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2060" yWindow="500" windowWidth="36980" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1420" yWindow="500" windowWidth="36980" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TEXT" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>id</t>
   </si>
@@ -107,51 +107,6 @@
   </si>
   <si>
     <t>ネットワークエラー</t>
-  </si>
-  <si>
-    <t>btn_start</t>
-  </si>
-  <si>
-    <t>시작 버튼</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>시작</t>
-  </si>
-  <si>
-    <t>開始</t>
-  </si>
-  <si>
-    <t>btn_quit</t>
-  </si>
-  <si>
-    <t>종료 버튼</t>
-  </si>
-  <si>
-    <t>Quit</t>
-  </si>
-  <si>
-    <t>종료</t>
-  </si>
-  <si>
-    <t>終了</t>
-  </si>
-  <si>
-    <t>loading</t>
-  </si>
-  <si>
-    <t>로딩 중</t>
-  </si>
-  <si>
-    <t>Loading...</t>
-  </si>
-  <si>
-    <t>로딩 중...</t>
-  </si>
-  <si>
-    <t>読み込み中...</t>
   </si>
 </sst>
 </file>
@@ -535,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -640,62 +595,11 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>43</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E9" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/input/Domains/Common/StringTable.xlsx
+++ b/input/Domains/Common/StringTable.xlsx
@@ -1,137 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Common/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702233DE-44E9-B34C-B4BD-9F0B88918A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1420" yWindow="500" windowWidth="36980" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1420" yWindow="500" windowWidth="36980" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TEXT" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEXT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>English</t>
-  </si>
-  <si>
-    <t>Korean</t>
-  </si>
-  <si>
-    <t>Japanese</t>
-  </si>
-  <si>
-    <t>greeting</t>
-  </si>
-  <si>
-    <t>인사말</t>
-  </si>
-  <si>
-    <t>Hello</t>
-  </si>
-  <si>
-    <t>안녕하세요</t>
-  </si>
-  <si>
-    <t>こんにちは</t>
-  </si>
-  <si>
-    <t>farewell</t>
-  </si>
-  <si>
-    <t>작별 인사</t>
-  </si>
-  <si>
-    <t>Goodbye</t>
-  </si>
-  <si>
-    <t>안녕히 가세요</t>
-  </si>
-  <si>
-    <t>さようなら</t>
-  </si>
-  <si>
-    <t>welcome</t>
-  </si>
-  <si>
-    <t>환영 메시지</t>
-  </si>
-  <si>
-    <t>Welcome</t>
-  </si>
-  <si>
-    <t>환영합니다</t>
-  </si>
-  <si>
-    <t>ようこそ</t>
-  </si>
-  <si>
-    <t>thanks</t>
-  </si>
-  <si>
-    <t>감사 인사</t>
-  </si>
-  <si>
-    <t>Thank you</t>
-  </si>
-  <si>
-    <t>감사합니다</t>
-  </si>
-  <si>
-    <t>ありがとう</t>
-  </si>
-  <si>
-    <t>error_network</t>
-  </si>
-  <si>
-    <t>네트워크 오류</t>
-  </si>
-  <si>
-    <t>Network error</t>
-  </si>
-  <si>
-    <t>ネットワークエラー</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -150,21 +53,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -489,117 +451,177 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Korean</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>greeting</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>인사말</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hello</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>안녕하세요</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>こんにちは</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>farewell</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>작별 인사</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Goodbye</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>안녕히 가세요</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>さようなら</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>welcome</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>환영 메시지</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Welcome</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>환영합니다</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ようこそ</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thanks</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>감사 인사</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Thank you</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>감사합니다</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ありがとう</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>error_network</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>네트워크 오류</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Network error</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>네트워크 오류</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ネットワークエラー</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:E6" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>